--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
+++ b/docs/dossiers/dossier-paris-3eme-arrondissement-3db05df8.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
